--- a/data/auction_2026-10-21.xlsx
+++ b/data/auction_2026-10-21.xlsx
@@ -21,16 +21,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -41,7 +38,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -49,21 +46,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -433,102 +421,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>买入价</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>竞价涨幅%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>竞价量占昨日%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>策略数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>同板块强势数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>综合评分</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>竞价强度</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>竞价量能</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>日线趋势</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>涨停基因</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>板块共振</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>止盈价</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>目标价</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>止损价</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>选中原因</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>风险提示</t>
         </is>
@@ -2338,10 +2326,10 @@
         <v>11.11</v>
       </c>
       <c r="Q27" t="n">
-        <v>9.800000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="R27" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="S27" t="inlineStr">
         <is>
@@ -2408,10 +2396,10 @@
         <v>6.49</v>
       </c>
       <c r="Q28" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="R28" t="n">
-        <v>1.67</v>
+        <v>1.03</v>
       </c>
       <c r="S28" t="inlineStr">
         <is>
@@ -2968,10 +2956,10 @@
         <v>7.13</v>
       </c>
       <c r="Q36" t="n">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="R36" t="n">
-        <v>1.68</v>
+        <v>1.1</v>
       </c>
       <c r="S36" t="inlineStr">
         <is>
@@ -4669,102 +4657,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>买入价</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>竞价涨幅%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>竞价量占昨日%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>策略数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>同板块强势数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>综合评分</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>竞价强度</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>竞价量能</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>日线趋势</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>涨停基因</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>板块共振</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>止盈价</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>目标价</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>止损价</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>选中原因</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>风险提示</t>
         </is>
@@ -5275,102 +5263,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>买入价</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>竞价涨幅%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>竞价量占昨日%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>策略数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>同板块强势数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>综合评分</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>竞价强度</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>竞价量能</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>日线趋势</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>涨停基因</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>板块共振</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>止盈价</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>目标价</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>止损价</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>选中原因</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>风险提示</t>
         </is>
@@ -5811,102 +5799,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>买入价</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>竞价涨幅%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>竞价量占昨日%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>策略数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>同板块强势数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>综合评分</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>竞价强度</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>竞价量能</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>日线趋势</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>涨停基因</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>板块共振</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>止盈价</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>目标价</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>止损价</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>选中原因</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>风险提示</t>
         </is>
@@ -7047,102 +7035,102 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>代码</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>名称</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>买入价</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>竞价涨幅%</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>竞价量占昨日%</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>命中策略</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>策略数</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>同板块强势数</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>综合评分</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>竞价强度</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>竞价量能</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>日线趋势</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>涨停基因</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>板块共振</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>止盈价</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>目标价</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>止损价</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>盈亏比</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="S1" t="inlineStr">
         <is>
           <t>选中原因</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="T1" t="inlineStr">
         <is>
           <t>风险提示</t>
         </is>
@@ -8742,10 +8730,10 @@
         <v>11.11</v>
       </c>
       <c r="Q24" t="n">
-        <v>9.800000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="R24" t="n">
-        <v>1.7</v>
+        <v>1.04</v>
       </c>
       <c r="S24" t="inlineStr">
         <is>
@@ -8812,10 +8800,10 @@
         <v>6.49</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.72</v>
+        <v>5.61</v>
       </c>
       <c r="R25" t="n">
-        <v>1.67</v>
+        <v>1.03</v>
       </c>
       <c r="S25" t="inlineStr">
         <is>
@@ -9372,10 +9360,10 @@
         <v>7.13</v>
       </c>
       <c r="Q33" t="n">
-        <v>6.29</v>
+        <v>6.19</v>
       </c>
       <c r="R33" t="n">
-        <v>1.68</v>
+        <v>1.1</v>
       </c>
       <c r="S33" t="inlineStr">
         <is>
